--- a/tests/fixtures/out/export_engine_cross.xlsx
+++ b/tests/fixtures/out/export_engine_cross.xlsx
@@ -465,11 +465,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="F7">
-        <v>3000</v>
-      </c>
-    </row>
+    <row r="7" spans="1:6"/>
     <row r="8" spans="1:6">
       <c r="A8">
         <v>2</v>
@@ -546,11 +542,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="F16">
-        <v>500</v>
-      </c>
-    </row>
+    <row r="16" spans="1:6"/>
     <row r="17" spans="1:4">
       <c r="A17">
         <v>5</v>
@@ -566,14 +558,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="B4:B7"/>
     <mergeCell ref="C4:C7"/>
     <mergeCell ref="D4:D7"/>
     <mergeCell ref="F4:F5"/>
+    <mergeCell ref="F6:F7"/>
     <mergeCell ref="F13:F14"/>
+    <mergeCell ref="F15:F16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
